--- a/artfynd/Kravattensliden artfynd.xlsx
+++ b/artfynd/Kravattensliden artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>131738083</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>131738082</v>
       </c>
       <c r="B15" t="n">
-        <v>80432</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>131740439</v>
       </c>
       <c r="B18" t="n">
-        <v>80461</v>
+        <v>80493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>131732977</v>
       </c>
       <c r="B21" t="n">
-        <v>80467</v>
+        <v>80499</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>131739856</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>131734574</v>
       </c>
       <c r="B26" t="n">
-        <v>80392</v>
+        <v>80438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>131736590</v>
       </c>
       <c r="B79" t="n">
-        <v>80433</v>
+        <v>80489</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>131740440</v>
       </c>
       <c r="B119" t="n">
-        <v>80461</v>
+        <v>80493</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>131734575</v>
       </c>
       <c r="B130" t="n">
-        <v>80392</v>
+        <v>80438</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>131739580</v>
       </c>
       <c r="B159" t="n">
-        <v>91909</v>
+        <v>91974</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>131739857</v>
       </c>
       <c r="B272" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>131738631</v>
       </c>
       <c r="B529" t="n">
-        <v>79359</v>
+        <v>79405</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -55204,7 +55204,7 @@
         <v>131738632</v>
       </c>
       <c r="B530" t="n">
-        <v>79359</v>
+        <v>79405</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>131739581</v>
       </c>
       <c r="B533" t="n">
-        <v>91909</v>
+        <v>91974</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>131739582</v>
       </c>
       <c r="B534" t="n">
-        <v>91909</v>
+        <v>91974</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -55709,7 +55709,7 @@
         <v>131735901</v>
       </c>
       <c r="B535" t="n">
-        <v>91923</v>
+        <v>91988</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>131736932</v>
       </c>
       <c r="B536" t="n">
-        <v>92369</v>
+        <v>92406</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -57034,7 +57034,7 @@
         <v>131738808</v>
       </c>
       <c r="B548" t="n">
-        <v>91872</v>
+        <v>91937</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>131739858</v>
       </c>
       <c r="B556" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
